--- a/Produccion.xlsx
+++ b/Produccion.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F131C2F-7114-4677-94B4-F42D880D686E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2D1A3F2-9B81-43C3-BE84-8217519E6E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28560" windowHeight="13905" xr2:uid="{A22C7B05-6B0A-4116-A99A-60EDDEA67682}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
   <si>
     <t>Mes</t>
   </si>
@@ -135,6 +135,21 @@
     <t>Falla Tolva # 2 Granalla</t>
   </si>
   <si>
+    <t>Granalla racks kimsu flujo lento</t>
+  </si>
+  <si>
+    <t>240 min solo 1 person aen granalla</t>
+  </si>
+  <si>
+    <t>Espera de priorida de embarque 230926-8AM</t>
+  </si>
+  <si>
+    <t>Granalla Heyang</t>
+  </si>
+  <si>
+    <t>Recoleccion de granalla por cambio de coples</t>
+  </si>
+  <si>
     <t>Corte Programado</t>
   </si>
   <si>
@@ -193,6 +208,18 @@
   </si>
   <si>
     <t>Falta de requerimiento para Laser</t>
+  </si>
+  <si>
+    <t>Flujo lento retrabajo channels</t>
+  </si>
+  <si>
+    <t>Se detiene actividad de colocacion de llantas Kimsu</t>
+  </si>
+  <si>
+    <t>Aprobacion de gap por parte de clinete Channels</t>
+  </si>
+  <si>
+    <t>Aprovacion dibujo por parte de cliente Tolva</t>
   </si>
 </sst>
 </file>
@@ -622,9 +649,9 @@
     <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.7109375" customWidth="1"/>
     <col min="12" max="12" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.42578125" customWidth="1"/>
+    <col min="14" max="14" width="32.42578125" customWidth="1"/>
+    <col min="15" max="15" width="39.42578125" customWidth="1"/>
     <col min="16" max="17" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1059,7 +1086,9 @@
       <c r="N10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="4"/>
+      <c r="O10" t="s">
+        <v>31</v>
+      </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
     </row>
@@ -1076,20 +1105,40 @@
         <f t="shared" si="3"/>
         <v>46287</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
+      <c r="E11" s="4">
+        <v>7</v>
+      </c>
+      <c r="F11" s="4">
+        <v>6</v>
+      </c>
+      <c r="G11" s="4">
+        <v>6</v>
+      </c>
+      <c r="H11" s="4">
+        <v>8</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="4"/>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1.2E-2</v>
+      </c>
+      <c r="M11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
@@ -1106,20 +1155,40 @@
         <f t="shared" si="3"/>
         <v>46288</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="5" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
+      <c r="E12" s="4">
+        <v>7</v>
+      </c>
+      <c r="F12" s="4">
+        <v>6</v>
+      </c>
+      <c r="G12" s="4">
+        <v>6</v>
+      </c>
+      <c r="H12" s="4">
+        <v>8</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="4"/>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J12" s="4">
+        <v>30</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0.84</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
@@ -4109,7 +4178,10 @@
     <col min="11" max="12" width="9.140625"/>
     <col min="13" max="13" width="10.140625" customWidth="1"/>
     <col min="15" max="16" width="5.85546875" customWidth="1"/>
-    <col min="17" max="21" width="20" customWidth="1"/>
+    <col min="17" max="17" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:21" ht="45.75">
@@ -4123,22 +4195,22 @@
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>5</v>
@@ -4223,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
@@ -4284,10 +4356,10 @@
         <v>2E-3</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
@@ -4401,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
@@ -4461,13 +4533,13 @@
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
@@ -4523,7 +4595,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
@@ -4579,10 +4651,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
@@ -4639,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
@@ -4659,24 +4731,52 @@
         <f t="shared" si="2"/>
         <v>46287</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="5" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="4"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <v>4</v>
+      </c>
+      <c r="H11" s="4">
+        <v>4</v>
+      </c>
+      <c r="I11" s="4">
+        <v>9</v>
+      </c>
+      <c r="J11" s="4">
+        <v>9</v>
+      </c>
+      <c r="K11" s="4">
+        <v>7</v>
+      </c>
+      <c r="L11" s="4">
+        <v>7</v>
+      </c>
+      <c r="M11" s="5">
+        <f>+((H11/G11)+(J11/I11))/2</f>
+        <v>1</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5">
+        <v>1</v>
+      </c>
+      <c r="P11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
     </row>
@@ -4693,24 +4793,52 @@
         <f t="shared" si="2"/>
         <v>46288</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="5" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N12" s="4"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
+      <c r="E12" s="4">
+        <v>80</v>
+      </c>
+      <c r="F12" s="4">
+        <v>80</v>
+      </c>
+      <c r="G12" s="4">
+        <v>113</v>
+      </c>
+      <c r="H12" s="4">
+        <v>110</v>
+      </c>
+      <c r="I12" s="4">
+        <v>3</v>
+      </c>
+      <c r="J12" s="4">
+        <v>2</v>
+      </c>
+      <c r="K12" s="4">
+        <v>6</v>
+      </c>
+      <c r="L12" s="4">
+        <v>7</v>
+      </c>
+      <c r="M12" s="5">
+        <f t="shared" si="3"/>
+        <v>0.88003933136676504</v>
+      </c>
+      <c r="N12" s="4">
+        <v>1090</v>
+      </c>
+      <c r="O12" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="P12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
     </row>
